--- a/港岛-赤柱-50 Stanley Village Road/50 Stanley Village Road_销控明细表.xlsx
+++ b/港岛-赤柱-50 Stanley Village Road/50 Stanley Village Road_销控明细表.xlsx
@@ -111,7 +111,7 @@
       <sz val="8"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -154,6 +154,12 @@
         <bgColor rgb="00FFC000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E5E5E5"/>
+        <bgColor rgb="00E5E5E5"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -181,7 +187,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -232,6 +238,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -599,7 +608,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -832,7 +841,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>3号屋</t>
+          <t>5号屋</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -847,11 +856,11 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>4+房</t>
+          <t>3房</t>
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>3179</v>
+        <v>2760</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -860,14 +869,14 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2015-04-29</t>
+          <t>2019-04-15</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
-        <v>169294000</v>
+        <v>168800000</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>53254</v>
+        <v>61159</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
@@ -875,10 +884,10 @@
         </is>
       </c>
       <c r="K5" s="5" t="n">
-        <v>169294000</v>
+        <v>168800000</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>53254</v>
+        <v>61159</v>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
@@ -894,7 +903,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>5号屋</t>
+          <t>6号屋</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -913,7 +922,7 @@
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>2760</v>
+        <v>2725</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -922,14 +931,14 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2019-04-15</t>
+          <t>2015-05-05</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
-        <v>168800000</v>
+        <v>127464000</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>61159</v>
+        <v>46776</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
@@ -937,10 +946,10 @@
         </is>
       </c>
       <c r="K6" s="5" t="n">
-        <v>168800000</v>
+        <v>127464000</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>61159</v>
+        <v>46776</v>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
@@ -956,7 +965,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>6号屋</t>
+          <t>7号屋</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -984,14 +993,14 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2015-05-05</t>
+          <t>2015-05-21</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
-        <v>127464000</v>
+        <v>146452000</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>46776</v>
+        <v>53744</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
@@ -999,10 +1008,10 @@
         </is>
       </c>
       <c r="K7" s="5" t="n">
-        <v>127464000</v>
+        <v>146452000</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>46776</v>
+        <v>53744</v>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
@@ -1018,7 +1027,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>7号屋</t>
+          <t>8号屋</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -1037,7 +1046,7 @@
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>2725</v>
+        <v>2895</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -1046,14 +1055,14 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2015-05-21</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
-        <v>146452000</v>
+        <v>106800000</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>53744</v>
+        <v>36891</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
@@ -1061,10 +1070,10 @@
         </is>
       </c>
       <c r="K8" s="5" t="n">
-        <v>146452000</v>
+        <v>106800000</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>53744</v>
+        <v>36891</v>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
@@ -1080,7 +1089,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>8号屋</t>
+          <t>9号屋</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -1099,7 +1108,7 @@
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>2895</v>
+        <v>2725</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -1108,14 +1117,14 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2025-05-23</t>
+          <t>2015-05-14</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
-        <v>106800000</v>
+        <v>125772000</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>36891</v>
+        <v>46155</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
@@ -1123,10 +1132,10 @@
         </is>
       </c>
       <c r="K9" s="5" t="n">
-        <v>106800000</v>
+        <v>125772000</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>36891</v>
+        <v>46155</v>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
@@ -1142,7 +1151,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>9号屋</t>
+          <t>10号屋</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1170,14 +1179,14 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2015-05-14</t>
+          <t>2017-11-22</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
-        <v>125772000</v>
+        <v>145500000</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>46155</v>
+        <v>53394</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
@@ -1185,10 +1194,10 @@
         </is>
       </c>
       <c r="K10" s="5" t="n">
-        <v>125772000</v>
+        <v>145500000</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>46155</v>
+        <v>53394</v>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
@@ -1204,7 +1213,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>10号屋</t>
+          <t>11号屋</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -1232,14 +1241,14 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2017-11-22</t>
+          <t>2015-05-08</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
-        <v>145500000</v>
+        <v>126148000</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>53394</v>
+        <v>46293</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
@@ -1247,10 +1256,10 @@
         </is>
       </c>
       <c r="K11" s="5" t="n">
-        <v>145500000</v>
+        <v>126148000</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>53394</v>
+        <v>46293</v>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
@@ -1266,7 +1275,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>11号屋</t>
+          <t>12号屋</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1285,7 +1294,7 @@
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>2725</v>
+        <v>2713</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -1294,14 +1303,14 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2015-05-08</t>
+          <t>2015-05-14</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
-        <v>126148000</v>
+        <v>122317000</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>46293</v>
+        <v>45086</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
@@ -1309,10 +1318,10 @@
         </is>
       </c>
       <c r="K12" s="5" t="n">
-        <v>126148000</v>
+        <v>122317000</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>46293</v>
+        <v>45086</v>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
@@ -1328,7 +1337,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>12号屋</t>
+          <t>15号屋</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -1347,7 +1356,7 @@
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>2713</v>
+        <v>2751</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -1356,14 +1365,14 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2015-05-14</t>
+          <t>2016-03-29</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
-        <v>122317000</v>
+        <v>135800000</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>45086</v>
+        <v>49364</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
@@ -1371,10 +1380,10 @@
         </is>
       </c>
       <c r="K13" s="5" t="n">
-        <v>122317000</v>
+        <v>135800000</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>45086</v>
+        <v>49364</v>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
@@ -1382,68 +1391,6 @@
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>15号屋</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>2751</v>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>2016-03-29</t>
-        </is>
-      </c>
-      <c r="H14" s="5" t="n">
-        <v>135800000</v>
-      </c>
-      <c r="I14" s="5" t="n">
-        <v>49364</v>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K14" s="5" t="n">
-        <v>135800000</v>
-      </c>
-      <c r="L14" s="5" t="n">
-        <v>49364</v>
-      </c>
-      <c r="M14" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N14" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -1518,7 +1465,7 @@
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="11" t="inlineStr">
         <is>
-          <t>12 套</t>
+          <t>11 套</t>
         </is>
       </c>
       <c r="B3" s="12" t="inlineStr">
@@ -1533,7 +1480,7 @@
       </c>
       <c r="D3" s="14" t="inlineStr">
         <is>
-          <t>11 套</t>
+          <t>10 套</t>
         </is>
       </c>
       <c r="E3" s="15" t="inlineStr">
@@ -1610,15 +1557,6 @@
       </c>
       <c r="D6" s="17" t="inlineStr">
         <is>
-          <t>3号屋
-3179呎 (4+房)
-(15年-04月-29日)
-$1.69亿
-$53,254/呎</t>
-        </is>
-      </c>
-      <c r="E6" s="17" t="inlineStr">
-        <is>
           <t>5号屋
 2760呎 (3房)
 (19年-04月-15日)
@@ -1626,7 +1564,7 @@
 $61,159/呎</t>
         </is>
       </c>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="E6" s="17" t="inlineStr">
         <is>
           <t>6号屋
 2725呎 (3房)
@@ -1635,7 +1573,7 @@
 $46,776/呎</t>
         </is>
       </c>
-      <c r="G6" s="17" t="inlineStr">
+      <c r="F6" s="17" t="inlineStr">
         <is>
           <t>7号屋
 2725呎 (3房)
@@ -1644,14 +1582,7 @@
 $53,744/呎</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="80" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>第 2 行</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="G6" s="17" t="inlineStr">
         <is>
           <t>8号屋
 2895呎 (3房)
@@ -1660,7 +1591,14 @@
 $36,891/呎</t>
         </is>
       </c>
-      <c r="C7" s="17" t="inlineStr">
+    </row>
+    <row r="7" ht="80" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>第 2 行</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>9号屋
 2725呎 (3房)
@@ -1669,7 +1607,7 @@
 $46,155/呎</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="C7" s="17" t="inlineStr">
         <is>
           <t>10号屋
 2725呎 (3房)
@@ -1678,7 +1616,7 @@
 $53,394/呎</t>
         </is>
       </c>
-      <c r="E7" s="17" t="inlineStr">
+      <c r="D7" s="17" t="inlineStr">
         <is>
           <t>11号屋
 2725呎 (3房)
@@ -1687,7 +1625,7 @@
 $46,293/呎</t>
         </is>
       </c>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="E7" s="17" t="inlineStr">
         <is>
           <t>12号屋
 2713呎 (3房)
@@ -1696,7 +1634,7 @@
 $45,086/呎</t>
         </is>
       </c>
-      <c r="G7" s="17" t="inlineStr">
+      <c r="F7" s="17" t="inlineStr">
         <is>
           <t>15号屋
 2751呎 (3房)
@@ -1705,6 +1643,7 @@
 $49,364/呎</t>
         </is>
       </c>
+      <c r="G7" s="18" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/港岛-赤柱-50 Stanley Village Road/50 Stanley Village Road_销控明细表.xlsx
+++ b/港岛-赤柱-50 Stanley Village Road/50 Stanley Village Road_销控明细表.xlsx
@@ -111,7 +111,7 @@
       <sz val="8"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -154,12 +154,6 @@
         <bgColor rgb="00FFC000"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -187,7 +181,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -238,9 +232,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -608,7 +599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -841,7 +832,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>5号屋</t>
+          <t>3号屋</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -856,11 +847,11 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>3房</t>
+          <t>4+房</t>
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>2760</v>
+        <v>3179</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -869,14 +860,14 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2019-04-15</t>
+          <t>2015-04-29</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
-        <v>168800000</v>
+        <v>169294000</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>61159</v>
+        <v>53254</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
@@ -884,10 +875,10 @@
         </is>
       </c>
       <c r="K5" s="5" t="n">
-        <v>168800000</v>
+        <v>169294000</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>61159</v>
+        <v>53254</v>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
@@ -903,7 +894,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>6号屋</t>
+          <t>5号屋</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -922,7 +913,7 @@
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>2725</v>
+        <v>2760</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -931,14 +922,14 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2015-05-05</t>
+          <t>2019-04-15</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
-        <v>127464000</v>
+        <v>168800000</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>46776</v>
+        <v>61159</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
@@ -946,10 +937,10 @@
         </is>
       </c>
       <c r="K6" s="5" t="n">
-        <v>127464000</v>
+        <v>168800000</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>46776</v>
+        <v>61159</v>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
@@ -965,7 +956,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>7号屋</t>
+          <t>6号屋</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -993,14 +984,14 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2015-05-21</t>
+          <t>2015-05-05</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
-        <v>146452000</v>
+        <v>127464000</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>53744</v>
+        <v>46776</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
@@ -1008,10 +999,10 @@
         </is>
       </c>
       <c r="K7" s="5" t="n">
-        <v>146452000</v>
+        <v>127464000</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>53744</v>
+        <v>46776</v>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
@@ -1027,7 +1018,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>8号屋</t>
+          <t>7号屋</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -1046,7 +1037,7 @@
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>2895</v>
+        <v>2725</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -1055,14 +1046,14 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2025-05-23</t>
+          <t>2015-05-21</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
-        <v>106800000</v>
+        <v>146452000</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>36891</v>
+        <v>53744</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
@@ -1070,10 +1061,10 @@
         </is>
       </c>
       <c r="K8" s="5" t="n">
-        <v>106800000</v>
+        <v>146452000</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>36891</v>
+        <v>53744</v>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
@@ -1089,7 +1080,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>9号屋</t>
+          <t>8号屋</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -1108,7 +1099,7 @@
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>2725</v>
+        <v>2895</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -1117,14 +1108,14 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2015-05-14</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
-        <v>125772000</v>
+        <v>106800000</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>46155</v>
+        <v>36891</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
@@ -1132,10 +1123,10 @@
         </is>
       </c>
       <c r="K9" s="5" t="n">
-        <v>125772000</v>
+        <v>106800000</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>46155</v>
+        <v>36891</v>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
@@ -1151,7 +1142,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>10号屋</t>
+          <t>9号屋</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1179,14 +1170,14 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2017-11-22</t>
+          <t>2015-05-14</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
-        <v>145500000</v>
+        <v>125772000</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>53394</v>
+        <v>46155</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
@@ -1194,10 +1185,10 @@
         </is>
       </c>
       <c r="K10" s="5" t="n">
-        <v>145500000</v>
+        <v>125772000</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>53394</v>
+        <v>46155</v>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
@@ -1213,7 +1204,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>11号屋</t>
+          <t>10号屋</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -1241,14 +1232,14 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2015-05-08</t>
+          <t>2017-11-22</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
-        <v>126148000</v>
+        <v>145500000</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>46293</v>
+        <v>53394</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
@@ -1256,10 +1247,10 @@
         </is>
       </c>
       <c r="K11" s="5" t="n">
-        <v>126148000</v>
+        <v>145500000</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>46293</v>
+        <v>53394</v>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
@@ -1275,7 +1266,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>12号屋</t>
+          <t>11号屋</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1294,7 +1285,7 @@
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>2713</v>
+        <v>2725</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -1303,14 +1294,14 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2015-05-14</t>
+          <t>2015-05-08</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
-        <v>122317000</v>
+        <v>126148000</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>45086</v>
+        <v>46293</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
@@ -1318,10 +1309,10 @@
         </is>
       </c>
       <c r="K12" s="5" t="n">
-        <v>122317000</v>
+        <v>126148000</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>45086</v>
+        <v>46293</v>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
@@ -1337,60 +1328,122 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
+          <t>12号屋</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>2713</v>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>2015-05-14</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>122317000</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>45086</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>122317000</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>45086</v>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
           <t>15号屋</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>3房</t>
         </is>
       </c>
-      <c r="E13" s="4" t="n">
+      <c r="E14" s="4" t="n">
         <v>2751</v>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t>已售</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="G14" s="3" t="inlineStr">
         <is>
           <t>2016-03-29</t>
         </is>
       </c>
-      <c r="H13" s="5" t="n">
+      <c r="H14" s="5" t="n">
         <v>135800000</v>
       </c>
-      <c r="I13" s="5" t="n">
+      <c r="I14" s="5" t="n">
         <v>49364</v>
       </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K13" s="5" t="n">
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="n">
         <v>135800000</v>
       </c>
-      <c r="L13" s="5" t="n">
+      <c r="L14" s="5" t="n">
         <v>49364</v>
       </c>
-      <c r="M13" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N13" s="3" t="inlineStr">
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -1465,22 +1518,22 @@
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="11" t="inlineStr">
         <is>
+          <t>12 套</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>1 套</t>
+        </is>
+      </c>
+      <c r="C3" s="13" t="inlineStr">
+        <is>
+          <t>0 套</t>
+        </is>
+      </c>
+      <c r="D3" s="14" t="inlineStr">
+        <is>
           <t>11 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>10 套</t>
         </is>
       </c>
       <c r="E3" s="15" t="inlineStr">
@@ -1557,6 +1610,15 @@
       </c>
       <c r="D6" s="17" t="inlineStr">
         <is>
+          <t>3号屋
+3179呎 (4+房)
+(15年-04月-29日)
+$1.69亿
+$53,254/呎</t>
+        </is>
+      </c>
+      <c r="E6" s="17" t="inlineStr">
+        <is>
           <t>5号屋
 2760呎 (3房)
 (19年-04月-15日)
@@ -1564,7 +1626,7 @@
 $61,159/呎</t>
         </is>
       </c>
-      <c r="E6" s="17" t="inlineStr">
+      <c r="F6" s="17" t="inlineStr">
         <is>
           <t>6号屋
 2725呎 (3房)
@@ -1573,7 +1635,7 @@
 $46,776/呎</t>
         </is>
       </c>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="G6" s="17" t="inlineStr">
         <is>
           <t>7号屋
 2725呎 (3房)
@@ -1582,7 +1644,14 @@
 $53,744/呎</t>
         </is>
       </c>
-      <c r="G6" s="17" t="inlineStr">
+    </row>
+    <row r="7" ht="80" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>第 2 行</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>8号屋
 2895呎 (3房)
@@ -1591,14 +1660,7 @@
 $36,891/呎</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="80" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>第 2 行</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="C7" s="17" t="inlineStr">
         <is>
           <t>9号屋
 2725呎 (3房)
@@ -1607,7 +1669,7 @@
 $46,155/呎</t>
         </is>
       </c>
-      <c r="C7" s="17" t="inlineStr">
+      <c r="D7" s="17" t="inlineStr">
         <is>
           <t>10号屋
 2725呎 (3房)
@@ -1616,7 +1678,7 @@
 $53,394/呎</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="E7" s="17" t="inlineStr">
         <is>
           <t>11号屋
 2725呎 (3房)
@@ -1625,7 +1687,7 @@
 $46,293/呎</t>
         </is>
       </c>
-      <c r="E7" s="17" t="inlineStr">
+      <c r="F7" s="17" t="inlineStr">
         <is>
           <t>12号屋
 2713呎 (3房)
@@ -1634,7 +1696,7 @@
 $45,086/呎</t>
         </is>
       </c>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="G7" s="17" t="inlineStr">
         <is>
           <t>15号屋
 2751呎 (3房)
@@ -1643,7 +1705,6 @@
 $49,364/呎</t>
         </is>
       </c>
-      <c r="G7" s="18" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
